--- a/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
+++ b/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Scenario</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Worker Management</t>
+          <t>Manage Cost Centers</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
+++ b/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SolarWinds Service Desk Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADP Workforce Now Settings</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,63 +715,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGM450J1YK3FN478G7X08MGN</t>
+          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KGM450J1YK3FN478G7X08MGN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Provisioning Threshold</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>ADP Workforce Now Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KGM450J1YK3FN478G7X08MGN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KGM450J1YK3FN478G7X08MGN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,63 +781,63 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMF55H58M5ND9REFBS3NRMB5</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF55H58M5ND9REFBS3NRMB5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,120 +869,164 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMF55H58M5ND9REFBS3NRMB5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF55H58M5ND9REFBS3NRMB5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
+++ b/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
@@ -749,29 +749,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ADP Workforce Now Settings</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KGM450J1YK3FN478G7X08MGN</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KGM450J1YK3FN478G7X08MGN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Sensitive Fields -( Is this section required?)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMMRG3VN0V8HGZPHQVM51HGN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMRG3VN0V8HGZPHQVM51HGN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,41 +825,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMF55H58M5ND9REFBS3NRMB5</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF55H58M5ND9REFBS3NRMB5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMF55H58M5ND9REFBS3NRMB5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF55H58M5ND9REFBS3NRMB5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>

--- a/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
+++ b/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,29 +771,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sensitive Fields -( Is this section required?)</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Sensitive Fields -( Is this section required?)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMMRG3VN0V8HGZPHQVM51HGN</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMRG3VN0V8HGZPHQVM51HGN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,41 +847,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMF55H58M5ND9REFBS3NRMB5</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF55H58M5ND9REFBS3NRMB5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,98 +935,120 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMF55H58M5ND9REFBS3NRMB5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF55H58M5ND9REFBS3NRMB5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
+++ b/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sensitive Fields -( Is this section required?)</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">

--- a/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
+++ b/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Success Notifications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Failure Notifications</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,78 +913,78 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMF55H58M5ND9REFBS3NRMB5</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF55H58M5ND9REFBS3NRMB5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
     </row>

--- a/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
+++ b/site/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Cost Center Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01KQVMYBGQVNVAWK8JY6JC9VHE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KQVMYBGQVNVAWK8JY6JC9VHE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Provisioning Threshold</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,41 +737,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Provisioning Threshold</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,41 +825,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Success Notifications</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Failure Notifications</t>
+          <t>Success Notifications</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Failure Notifications</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,98 +957,120 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-iHCM-ADP-Workforce-Now-Cost-Center-Sync-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
